--- a/Spreadsheets and Logs/Validation.xlsx
+++ b/Spreadsheets and Logs/Validation.xlsx
@@ -419,6 +419,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -446,6 +449,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -459,12 +465,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -502,22 +502,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="B2">
-            <v>-5.0749108195304897E-3</v>
+            <v>-5.0749109999999997E-3</v>
           </cell>
           <cell r="C2">
-            <v>-0.181008040904999</v>
+            <v>-0.18100804100000001</v>
           </cell>
           <cell r="D2">
-            <v>-0.15141341090202301</v>
+            <v>-0.151413411</v>
           </cell>
           <cell r="E2">
-            <v>4.7349274158477797E-2</v>
+            <v>4.7349273999999997E-2</v>
           </cell>
           <cell r="F2">
-            <v>-7.1462162304669597E-4</v>
+            <v>-7.1462200000000004E-4</v>
           </cell>
           <cell r="G2">
-            <v>-6.9441180676221804E-4</v>
+            <v>-6.9441200000000005E-4</v>
           </cell>
         </row>
       </sheetData>
@@ -851,51 +851,51 @@
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="23" t="s">
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="25" t="s">
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="27"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="31"/>
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -1001,27 +1001,27 @@
       <c r="F3" s="14"/>
       <c r="G3" s="12">
         <f>[1]ATI_Sensor_Log!G2</f>
-        <v>-6.9441180676221804E-4</v>
+        <v>-6.9441200000000005E-4</v>
       </c>
       <c r="H3" s="13">
         <f>-1*[1]ATI_Sensor_Log!F2</f>
-        <v>7.1462162304669597E-4</v>
+        <v>7.1462200000000004E-4</v>
       </c>
       <c r="I3" s="13">
         <f>[1]ATI_Sensor_Log!E2</f>
-        <v>4.7349274158477797E-2</v>
+        <v>4.7349273999999997E-2</v>
       </c>
       <c r="J3" s="13">
         <f>[1]ATI_Sensor_Log!D2</f>
-        <v>-0.15141341090202301</v>
+        <v>-0.151413411</v>
       </c>
       <c r="K3" s="13">
         <f>-1*[1]ATI_Sensor_Log!C2</f>
-        <v>0.181008040904999</v>
+        <v>0.18100804100000001</v>
       </c>
       <c r="L3" s="13">
         <f>[1]ATI_Sensor_Log!B2</f>
-        <v>-5.0749108195304897E-3</v>
+        <v>-5.0749109999999997E-3</v>
       </c>
       <c r="M3" s="14"/>
       <c r="N3" s="12"/>
@@ -1033,27 +1033,27 @@
       <c r="T3" s="14"/>
       <c r="U3" s="2">
         <f>ABS(G3-N3)</f>
-        <v>6.9441180676221804E-4</v>
+        <v>6.9441200000000005E-4</v>
       </c>
       <c r="V3" s="1">
         <f t="shared" ref="V3:Z3" si="0">ABS(H3-O3)</f>
-        <v>7.1462162304669597E-4</v>
+        <v>7.1462200000000004E-4</v>
       </c>
       <c r="W3" s="1">
         <f t="shared" si="0"/>
-        <v>4.7349274158477797E-2</v>
+        <v>4.7349273999999997E-2</v>
       </c>
       <c r="X3" s="1">
         <f t="shared" si="0"/>
-        <v>0.15141341090202301</v>
+        <v>0.151413411</v>
       </c>
       <c r="Y3" s="1">
         <f t="shared" si="0"/>
-        <v>0.181008040904999</v>
+        <v>0.18100804100000001</v>
       </c>
       <c r="Z3" s="1">
         <f t="shared" si="0"/>
-        <v>5.0749108195304897E-3</v>
+        <v>5.0749109999999997E-3</v>
       </c>
       <c r="AA3" s="3"/>
     </row>
@@ -3357,7 +3357,7 @@
         <f>[1]ATI_Sensor_Log!G50</f>
         <v>0</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="16">
         <f>-1*[1]ATI_Sensor_Log!F50</f>
         <v>0</v>
       </c>
@@ -3369,7 +3369,7 @@
         <f>[1]ATI_Sensor_Log!D50</f>
         <v>0</v>
       </c>
-      <c r="K51" s="30">
+      <c r="K51" s="16">
         <f>-1*[1]ATI_Sensor_Log!C50</f>
         <v>0</v>
       </c>
@@ -3413,51 +3413,51 @@
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="28" t="s">
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="25" t="s">
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
-      <c r="AA1" s="27"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="31"/>
       <c r="AB1" s="7"/>
       <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
+      <c r="AF1" s="19"/>
+      <c r="AG1" s="19"/>
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="19"/>
+      <c r="AK1" s="19"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
@@ -3563,27 +3563,27 @@
       <c r="F3" s="14"/>
       <c r="G3" s="12">
         <f>[1]ATI_Sensor_Log!G2</f>
-        <v>-6.9441180676221804E-4</v>
+        <v>-6.9441200000000005E-4</v>
       </c>
       <c r="H3" s="13">
         <f>-1*[1]ATI_Sensor_Log!F2</f>
-        <v>7.1462162304669597E-4</v>
+        <v>7.1462200000000004E-4</v>
       </c>
       <c r="I3" s="13">
         <f>[1]ATI_Sensor_Log!E2</f>
-        <v>4.7349274158477797E-2</v>
+        <v>4.7349273999999997E-2</v>
       </c>
       <c r="J3" s="13">
         <f>[1]ATI_Sensor_Log!D2</f>
-        <v>-0.15141341090202301</v>
+        <v>-0.151413411</v>
       </c>
       <c r="K3" s="13">
         <f>-1*[1]ATI_Sensor_Log!C2</f>
-        <v>0.181008040904999</v>
+        <v>0.18100804100000001</v>
       </c>
       <c r="L3" s="13">
         <f>[1]ATI_Sensor_Log!B2</f>
-        <v>-5.0749108195304897E-3</v>
+        <v>-5.0749109999999997E-3</v>
       </c>
       <c r="M3" s="14"/>
       <c r="N3" s="12"/>
@@ -3835,7 +3835,7 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="31"/>
+      <c r="T8" s="17"/>
       <c r="U8" s="2"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
@@ -3882,7 +3882,7 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="31"/>
+      <c r="T9" s="17"/>
       <c r="U9" s="2"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -3929,7 +3929,7 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="T10" s="31"/>
+      <c r="T10" s="17"/>
       <c r="U10" s="2"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -3976,7 +3976,7 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
-      <c r="T11" s="31"/>
+      <c r="T11" s="17"/>
       <c r="U11" s="2"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
@@ -4023,7 +4023,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="31"/>
+      <c r="T12" s="17"/>
       <c r="U12" s="2"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -4070,7 +4070,7 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-      <c r="T13" s="31"/>
+      <c r="T13" s="17"/>
       <c r="U13" s="2"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
@@ -4117,7 +4117,7 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="31"/>
+      <c r="T14" s="17"/>
       <c r="U14" s="2"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
@@ -4164,7 +4164,7 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="31"/>
+      <c r="T15" s="17"/>
       <c r="U15" s="2"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
@@ -4211,7 +4211,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="31"/>
+      <c r="T16" s="17"/>
       <c r="U16" s="2"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -4258,7 +4258,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="31"/>
+      <c r="T17" s="17"/>
       <c r="U17" s="2"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -4305,7 +4305,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="31"/>
+      <c r="T18" s="17"/>
       <c r="U18" s="2"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -4352,7 +4352,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="31"/>
+      <c r="T19" s="17"/>
       <c r="U19" s="2"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -4399,7 +4399,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="31"/>
+      <c r="T20" s="17"/>
       <c r="U20" s="2"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -4446,7 +4446,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="31"/>
+      <c r="T21" s="17"/>
       <c r="U21" s="2"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -4493,7 +4493,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="31"/>
+      <c r="T22" s="17"/>
       <c r="U22" s="2"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -4540,7 +4540,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="31"/>
+      <c r="T23" s="17"/>
       <c r="U23" s="2"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -4587,7 +4587,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="31"/>
+      <c r="T24" s="17"/>
       <c r="U24" s="2"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -4634,7 +4634,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="31"/>
+      <c r="T25" s="17"/>
       <c r="U25" s="2"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -4681,7 +4681,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="31"/>
+      <c r="T26" s="17"/>
       <c r="U26" s="2"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -4728,7 +4728,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="31"/>
+      <c r="T27" s="17"/>
       <c r="U27" s="2"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -4775,7 +4775,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="31"/>
+      <c r="T28" s="17"/>
       <c r="U28" s="2"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -4822,7 +4822,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="31"/>
+      <c r="T29" s="17"/>
       <c r="U29" s="2"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -4869,7 +4869,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="31"/>
+      <c r="T30" s="17"/>
       <c r="U30" s="2"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -4916,7 +4916,7 @@
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="31"/>
+      <c r="T31" s="17"/>
       <c r="U31" s="2"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
@@ -4963,7 +4963,7 @@
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="31"/>
+      <c r="T32" s="17"/>
       <c r="U32" s="2"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -5010,7 +5010,7 @@
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="31"/>
+      <c r="T33" s="17"/>
       <c r="U33" s="2"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
@@ -5057,7 +5057,7 @@
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="31"/>
+      <c r="T34" s="17"/>
       <c r="U34" s="2"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
@@ -5104,7 +5104,7 @@
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
-      <c r="T35" s="31"/>
+      <c r="T35" s="17"/>
       <c r="U35" s="2"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
@@ -5151,7 +5151,7 @@
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
-      <c r="T36" s="31"/>
+      <c r="T36" s="17"/>
       <c r="U36" s="2"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
@@ -5198,7 +5198,7 @@
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="T37" s="31"/>
+      <c r="T37" s="17"/>
       <c r="U37" s="2"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
@@ -5245,7 +5245,7 @@
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="T38" s="31"/>
+      <c r="T38" s="17"/>
       <c r="U38" s="2"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
@@ -5292,7 +5292,7 @@
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="T39" s="31"/>
+      <c r="T39" s="17"/>
       <c r="U39" s="2"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
@@ -5339,7 +5339,7 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
-      <c r="T40" s="31"/>
+      <c r="T40" s="17"/>
       <c r="U40" s="2"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -5386,7 +5386,7 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
-      <c r="T41" s="31"/>
+      <c r="T41" s="17"/>
       <c r="U41" s="2"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -5433,7 +5433,7 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
-      <c r="T42" s="31"/>
+      <c r="T42" s="17"/>
       <c r="U42" s="2"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -5480,7 +5480,7 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
-      <c r="T43" s="31"/>
+      <c r="T43" s="17"/>
       <c r="U43" s="2"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -5527,7 +5527,7 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
-      <c r="T44" s="31"/>
+      <c r="T44" s="17"/>
       <c r="U44" s="2"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
@@ -5574,7 +5574,7 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
-      <c r="T45" s="31"/>
+      <c r="T45" s="17"/>
       <c r="U45" s="2"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
@@ -5621,7 +5621,7 @@
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
-      <c r="T46" s="31"/>
+      <c r="T46" s="17"/>
       <c r="U46" s="2"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
@@ -5668,7 +5668,7 @@
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
-      <c r="T47" s="31"/>
+      <c r="T47" s="17"/>
       <c r="U47" s="2"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
@@ -5715,7 +5715,7 @@
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
-      <c r="T48" s="31"/>
+      <c r="T48" s="17"/>
       <c r="U48" s="2"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
@@ -5762,7 +5762,7 @@
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
-      <c r="T49" s="31"/>
+      <c r="T49" s="17"/>
       <c r="U49" s="2"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
@@ -5809,7 +5809,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
-      <c r="T50" s="31"/>
+      <c r="T50" s="17"/>
       <c r="U50" s="2"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
@@ -5829,7 +5829,7 @@
         <f>[1]ATI_Sensor_Log!G50</f>
         <v>0</v>
       </c>
-      <c r="H51" s="30">
+      <c r="H51" s="16">
         <f>-1*[1]ATI_Sensor_Log!F50</f>
         <v>0</v>
       </c>
@@ -5841,7 +5841,7 @@
         <f>[1]ATI_Sensor_Log!D50</f>
         <v>0</v>
       </c>
-      <c r="K51" s="30">
+      <c r="K51" s="16">
         <f>-1*[1]ATI_Sensor_Log!C50</f>
         <v>0</v>
       </c>
@@ -5856,7 +5856,7 @@
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
-      <c r="T51" s="32"/>
+      <c r="T51" s="18"/>
       <c r="U51" s="4"/>
       <c r="V51" s="5"/>
       <c r="W51" s="5"/>
